--- a/donors.xlsx
+++ b/donors.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/design/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OK\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33910D3D-5187-E145-9841-AC0E8651AF03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27820" yWindow="500" windowWidth="25640" windowHeight="26380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="27816" yWindow="504" windowWidth="25644" windowHeight="26376"/>
   </bookViews>
   <sheets>
     <sheet name="상단 명판" sheetId="6" r:id="rId1"/>
@@ -25,7 +24,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'기부자월 명단'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'상단 명판'!$5:$5</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -42,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2273" uniqueCount="1402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2273" uniqueCount="1404">
   <si>
     <t>금액</t>
   </si>
@@ -1067,7 +1066,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="KozGoPro-Regular"/>
-        <charset val="128"/>
+        <family val="2"/>
       </rPr>
       <t>具本</t>
     </r>
@@ -1093,7 +1092,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="KozGoPro-Regular"/>
-        <charset val="128"/>
+        <family val="2"/>
       </rPr>
       <t>前三星電子 日本本社 社長</t>
     </r>
@@ -4449,11 +4448,19 @@
     <t>100 미만</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
+  <si>
+    <t>OK배정장학재단</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>OK배정장학재단</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="#,##0&quot;円&quot;"/>
   </numFmts>
@@ -4541,13 +4548,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="KozGoPro-Regular"/>
-      <charset val="128"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="KozGoPro-Regular"/>
-      <charset val="128"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -4904,7 +4911,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="표준 2 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="표준 2 3" xfId="1"/>
   </cellStyles>
   <dxfs count="21">
     <dxf>
@@ -5519,22 +5526,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF7E9E50-17FF-024E-BBDD-64D549C4E21C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q68"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" customWidth="1"/>
-    <col min="4" max="4" width="4.1640625" customWidth="1"/>
-    <col min="5" max="5" width="7.33203125" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="25.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.1640625" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" customWidth="1"/>
-    <col min="9" max="9" width="10.6640625" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.796875" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" customWidth="1"/>
+    <col min="4" max="4" width="4.19921875" customWidth="1"/>
+    <col min="5" max="5" width="7.296875" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="25.19921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.19921875" customWidth="1"/>
+    <col min="8" max="8" width="12.296875" customWidth="1"/>
+    <col min="9" max="9" width="10.69921875" customWidth="1"/>
+    <col min="10" max="10" width="12.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="19">
+    <row r="1" spans="1:10" ht="20.399999999999999">
       <c r="D1" s="6" t="s">
         <v>278</v>
       </c>
@@ -5575,7 +5582,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="18">
+    <row r="6" spans="1:10">
       <c r="A6" s="41" t="s">
         <v>303</v>
       </c>
@@ -5591,10 +5598,10 @@
         <v>178</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>285</v>
+        <v>1402</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>299</v>
+        <v>1403</v>
       </c>
       <c r="H6" s="39"/>
       <c r="I6" s="5"/>
@@ -5625,7 +5632,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="18">
+    <row r="8" spans="1:10">
       <c r="C8" s="33"/>
       <c r="D8" s="4">
         <v>3</v>
@@ -5645,7 +5652,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="18">
+    <row r="9" spans="1:10">
       <c r="C9" s="33"/>
       <c r="D9" s="4">
         <v>4</v>
@@ -5661,7 +5668,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="18">
+    <row r="10" spans="1:10">
       <c r="B10" t="s">
         <v>1395</v>
       </c>
@@ -5680,7 +5687,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="18">
+    <row r="11" spans="1:10">
       <c r="C11" s="28"/>
       <c r="D11" s="4">
         <v>6</v>
@@ -5696,7 +5703,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="18">
+    <row r="12" spans="1:10">
       <c r="C12" s="28"/>
       <c r="D12" s="4">
         <v>7</v>
@@ -5712,7 +5719,7 @@
         <v>1396</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="32" customHeight="1">
+    <row r="13" spans="1:10" ht="31.95" customHeight="1">
       <c r="C13" s="28"/>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
@@ -5853,7 +5860,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="19" spans="2:17" ht="36">
+    <row r="19" spans="2:17" ht="34.799999999999997">
       <c r="B19" s="42" t="s">
         <v>1398</v>
       </c>
@@ -5948,7 +5955,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="23" spans="2:17" ht="32" customHeight="1">
+    <row r="23" spans="2:17" ht="31.95" customHeight="1">
       <c r="C23" s="30"/>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
@@ -5971,7 +5978,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="24" spans="2:17" ht="32" customHeight="1">
+    <row r="24" spans="2:17" ht="31.95" customHeight="1">
       <c r="C24" s="30"/>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
@@ -5994,7 +6001,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="25" spans="2:17" ht="42">
+    <row r="25" spans="2:17" ht="31.2">
       <c r="C25" s="30"/>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
@@ -6066,7 +6073,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="28" spans="2:17" ht="18">
+    <row r="28" spans="2:17">
       <c r="C28" s="30"/>
       <c r="D28" s="4">
         <f t="shared" si="0"/>
@@ -6085,7 +6092,7 @@
       <c r="I28" s="5"/>
       <c r="J28" s="4"/>
     </row>
-    <row r="29" spans="2:17" ht="23">
+    <row r="29" spans="2:17">
       <c r="C29" s="30"/>
       <c r="D29" s="4">
         <f t="shared" si="0"/>
@@ -6222,7 +6229,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="35" spans="2:10" ht="36">
+    <row r="35" spans="2:10" ht="34.799999999999997">
       <c r="C35" s="31"/>
       <c r="D35" s="4">
         <f t="shared" si="0"/>
@@ -6245,7 +6252,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="36" spans="2:10" ht="36">
+    <row r="36" spans="2:10" ht="34.799999999999997">
       <c r="C36" s="31"/>
       <c r="D36" s="4">
         <f t="shared" si="0"/>
@@ -6268,7 +6275,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="37" spans="2:10" ht="24">
+    <row r="37" spans="2:10">
       <c r="C37" s="31"/>
       <c r="D37" s="4">
         <f t="shared" si="0"/>
@@ -6287,7 +6294,7 @@
       <c r="I37" s="5"/>
       <c r="J37" s="4"/>
     </row>
-    <row r="38" spans="2:10" ht="18">
+    <row r="38" spans="2:10">
       <c r="C38" s="31"/>
       <c r="D38" s="4">
         <f t="shared" si="0"/>
@@ -6306,7 +6313,7 @@
       <c r="I38" s="5"/>
       <c r="J38" s="4"/>
     </row>
-    <row r="39" spans="2:10" ht="18">
+    <row r="39" spans="2:10">
       <c r="B39" t="s">
         <v>1400</v>
       </c>
@@ -6757,7 +6764,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="59" spans="3:10" ht="23">
+    <row r="59" spans="3:10">
       <c r="C59" s="32"/>
       <c r="D59" s="4">
         <f t="shared" si="0"/>
@@ -6778,7 +6785,7 @@
       </c>
       <c r="J59" s="4"/>
     </row>
-    <row r="60" spans="3:10" ht="23">
+    <row r="60" spans="3:10">
       <c r="C60" s="32"/>
       <c r="D60" s="4">
         <f t="shared" si="0"/>
@@ -6799,7 +6806,7 @@
       </c>
       <c r="J60" s="4"/>
     </row>
-    <row r="61" spans="3:10" ht="23">
+    <row r="61" spans="3:10">
       <c r="C61" s="32"/>
       <c r="D61" s="4">
         <f t="shared" si="0"/>
@@ -6820,7 +6827,7 @@
       </c>
       <c r="J61" s="4"/>
     </row>
-    <row r="62" spans="3:10" ht="23">
+    <row r="62" spans="3:10">
       <c r="C62" s="32"/>
       <c r="D62" s="4">
         <f t="shared" si="0"/>
@@ -6841,7 +6848,7 @@
       </c>
       <c r="J62" s="4"/>
     </row>
-    <row r="63" spans="3:10" ht="23">
+    <row r="63" spans="3:10">
       <c r="C63" s="32"/>
       <c r="D63" s="4">
         <f t="shared" si="0"/>
@@ -6862,7 +6869,7 @@
       </c>
       <c r="J63" s="4"/>
     </row>
-    <row r="64" spans="3:10" ht="23">
+    <row r="64" spans="3:10">
       <c r="C64" s="32"/>
       <c r="D64" s="4">
         <f t="shared" si="0"/>
@@ -6883,7 +6890,7 @@
       </c>
       <c r="J64" s="4"/>
     </row>
-    <row r="65" spans="3:10" ht="23">
+    <row r="65" spans="3:10">
       <c r="C65" s="32"/>
       <c r="D65" s="4">
         <f t="shared" si="0"/>
@@ -6904,7 +6911,7 @@
       </c>
       <c r="J65" s="4"/>
     </row>
-    <row r="66" spans="3:10" ht="23">
+    <row r="66" spans="3:10">
       <c r="C66" s="32"/>
       <c r="D66" s="4">
         <f t="shared" si="0"/>
@@ -6925,7 +6932,7 @@
       </c>
       <c r="J66" s="4"/>
     </row>
-    <row r="67" spans="3:10" ht="23">
+    <row r="67" spans="3:10">
       <c r="C67" s="32"/>
       <c r="D67" s="4">
         <f t="shared" si="0"/>
@@ -6979,16 +6986,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3841751B-3287-6F4F-AAD7-65255BB4589A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C1197"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="42"/>
-    <col min="2" max="2" width="31.1640625" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" customWidth="1"/>
+    <col min="1" max="1" width="10.796875" style="42"/>
+    <col min="2" max="2" width="31.19921875" customWidth="1"/>
+    <col min="3" max="3" width="17.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="54">
+    <row r="1" spans="1:3" ht="52.2">
       <c r="B1" s="43" t="s">
         <v>305</v>
       </c>
@@ -17364,16 +17371,16 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B58:B59">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B103">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B104">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -17381,22 +17388,22 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:XFA217"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" customWidth="1"/>
-    <col min="4" max="4" width="4.1640625" customWidth="1"/>
-    <col min="5" max="5" width="7.33203125" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="25.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.1640625" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" customWidth="1"/>
-    <col min="9" max="9" width="10.6640625" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.796875" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" customWidth="1"/>
+    <col min="4" max="4" width="4.19921875" customWidth="1"/>
+    <col min="5" max="5" width="7.296875" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="25.19921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.19921875" customWidth="1"/>
+    <col min="8" max="8" width="12.296875" customWidth="1"/>
+    <col min="9" max="9" width="10.69921875" customWidth="1"/>
+    <col min="10" max="10" width="12.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="19">
+    <row r="1" spans="1:10" ht="20.399999999999999">
       <c r="D1" s="6" t="s">
         <v>278</v>
       </c>
@@ -17437,7 +17444,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="18">
+    <row r="6" spans="1:10">
       <c r="A6" s="41" t="s">
         <v>303</v>
       </c>
@@ -17487,7 +17494,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="18">
+    <row r="8" spans="1:10">
       <c r="C8" s="33"/>
       <c r="D8" s="4">
         <v>3</v>
@@ -17507,7 +17514,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="18">
+    <row r="9" spans="1:10">
       <c r="C9" s="33"/>
       <c r="D9" s="4">
         <v>4</v>
@@ -17523,7 +17530,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="18">
+    <row r="10" spans="1:10">
       <c r="B10" t="s">
         <v>1395</v>
       </c>
@@ -17542,7 +17549,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="18">
+    <row r="11" spans="1:10">
       <c r="C11" s="28"/>
       <c r="D11" s="4">
         <v>6</v>
@@ -17558,7 +17565,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="18">
+    <row r="12" spans="1:10">
       <c r="C12" s="28"/>
       <c r="D12" s="4">
         <v>7</v>
@@ -17574,7 +17581,7 @@
         <v>1396</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="32" customHeight="1">
+    <row r="13" spans="1:10" ht="31.95" customHeight="1">
       <c r="C13" s="28"/>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
@@ -17715,7 +17722,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="19" spans="2:17" ht="36">
+    <row r="19" spans="2:17" ht="34.799999999999997">
       <c r="B19" s="42" t="s">
         <v>1398</v>
       </c>
@@ -17810,7 +17817,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="23" spans="2:17" ht="32" customHeight="1">
+    <row r="23" spans="2:17" ht="31.95" customHeight="1">
       <c r="C23" s="30"/>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
@@ -17833,7 +17840,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="24" spans="2:17" ht="32" customHeight="1">
+    <row r="24" spans="2:17" ht="31.95" customHeight="1">
       <c r="C24" s="30"/>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
@@ -17856,7 +17863,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="25" spans="2:17" ht="42">
+    <row r="25" spans="2:17" ht="31.2">
       <c r="C25" s="30"/>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
@@ -17928,7 +17935,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="28" spans="2:17" ht="18">
+    <row r="28" spans="2:17">
       <c r="C28" s="30"/>
       <c r="D28" s="4">
         <f t="shared" si="0"/>
@@ -17947,7 +17954,7 @@
       <c r="I28" s="5"/>
       <c r="J28" s="4"/>
     </row>
-    <row r="29" spans="2:17" ht="23">
+    <row r="29" spans="2:17">
       <c r="C29" s="30"/>
       <c r="D29" s="4">
         <f t="shared" si="0"/>
@@ -18084,7 +18091,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="35" spans="2:10" ht="36">
+    <row r="35" spans="2:10" ht="34.799999999999997">
       <c r="C35" s="31"/>
       <c r="D35" s="4">
         <f t="shared" si="0"/>
@@ -18107,7 +18114,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="36" spans="2:10" ht="36">
+    <row r="36" spans="2:10" ht="34.799999999999997">
       <c r="C36" s="31"/>
       <c r="D36" s="4">
         <f t="shared" si="0"/>
@@ -18130,7 +18137,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="37" spans="2:10" ht="24">
+    <row r="37" spans="2:10">
       <c r="C37" s="31"/>
       <c r="D37" s="4">
         <f t="shared" si="0"/>
@@ -18149,7 +18156,7 @@
       <c r="I37" s="5"/>
       <c r="J37" s="4"/>
     </row>
-    <row r="38" spans="2:10" ht="18">
+    <row r="38" spans="2:10">
       <c r="C38" s="31"/>
       <c r="D38" s="4">
         <f t="shared" si="0"/>
@@ -18168,7 +18175,7 @@
       <c r="I38" s="5"/>
       <c r="J38" s="4"/>
     </row>
-    <row r="39" spans="2:10" ht="18">
+    <row r="39" spans="2:10">
       <c r="B39" t="s">
         <v>1400</v>
       </c>
@@ -18619,7 +18626,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="59" spans="3:10" ht="23">
+    <row r="59" spans="3:10">
       <c r="C59" s="32"/>
       <c r="D59" s="4">
         <f t="shared" si="0"/>
@@ -18640,7 +18647,7 @@
       </c>
       <c r="J59" s="4"/>
     </row>
-    <row r="60" spans="3:10" ht="23">
+    <row r="60" spans="3:10">
       <c r="C60" s="32"/>
       <c r="D60" s="4">
         <f t="shared" si="0"/>
@@ -18661,7 +18668,7 @@
       </c>
       <c r="J60" s="4"/>
     </row>
-    <row r="61" spans="3:10" ht="23">
+    <row r="61" spans="3:10">
       <c r="C61" s="32"/>
       <c r="D61" s="4">
         <f t="shared" si="0"/>
@@ -18682,7 +18689,7 @@
       </c>
       <c r="J61" s="4"/>
     </row>
-    <row r="62" spans="3:10" ht="23">
+    <row r="62" spans="3:10">
       <c r="C62" s="32"/>
       <c r="D62" s="4">
         <f t="shared" si="0"/>
@@ -18703,7 +18710,7 @@
       </c>
       <c r="J62" s="4"/>
     </row>
-    <row r="63" spans="3:10" ht="23">
+    <row r="63" spans="3:10">
       <c r="C63" s="32"/>
       <c r="D63" s="4">
         <f t="shared" si="0"/>
@@ -18724,7 +18731,7 @@
       </c>
       <c r="J63" s="4"/>
     </row>
-    <row r="64" spans="3:10" ht="23">
+    <row r="64" spans="3:10">
       <c r="C64" s="32"/>
       <c r="D64" s="4">
         <f t="shared" si="0"/>
@@ -18745,7 +18752,7 @@
       </c>
       <c r="J64" s="4"/>
     </row>
-    <row r="65" spans="1:10" ht="23">
+    <row r="65" spans="1:10">
       <c r="C65" s="32"/>
       <c r="D65" s="4">
         <f t="shared" si="0"/>
@@ -18766,7 +18773,7 @@
       </c>
       <c r="J65" s="4"/>
     </row>
-    <row r="66" spans="1:10" ht="23">
+    <row r="66" spans="1:10">
       <c r="C66" s="32"/>
       <c r="D66" s="4">
         <f t="shared" si="0"/>
@@ -18787,7 +18794,7 @@
       </c>
       <c r="J66" s="4"/>
     </row>
-    <row r="67" spans="1:10" ht="23">
+    <row r="67" spans="1:10">
       <c r="C67" s="32"/>
       <c r="D67" s="4">
         <f t="shared" si="0"/>
@@ -22241,55 +22248,55 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D13:K201">
+  <sortState ref="D13:K201">
     <sortCondition descending="1" ref="I13:I201"/>
     <sortCondition ref="F13:F201"/>
   </sortState>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="F52">
-    <cfRule type="duplicateValues" dxfId="18" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F53">
-    <cfRule type="duplicateValues" dxfId="17" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F97">
-    <cfRule type="duplicateValues" dxfId="16" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F119">
-    <cfRule type="duplicateValues" dxfId="15" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F124:F125">
-    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F144">
-    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F166:F167">
-    <cfRule type="duplicateValues" dxfId="12" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F168">
-    <cfRule type="duplicateValues" dxfId="11" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F169">
-    <cfRule type="duplicateValues" dxfId="10" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F170">
-    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F207">
-    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G97:H97">
-    <cfRule type="duplicateValues" dxfId="7" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G124:H125">
-    <cfRule type="duplicateValues" dxfId="6" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G170:H170">
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G171:H171">
-    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="62" orientation="portrait" r:id="rId1"/>
